--- a/BillScanTrackerAppium/Test_Results/android-appium-report.xlsx
+++ b/BillScanTrackerAppium/Test_Results/android-appium-report.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2504" uniqueCount="866">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2504" uniqueCount="867">
   <si>
     <t>Metric Name</t>
   </si>
@@ -45,7 +45,7 @@
     <t>Timestamp</t>
   </si>
   <si>
-    <t>2026-07-27T09:02:16.382Z</t>
+    <t>2026-07-29T03:40:58.478Z</t>
   </si>
   <si>
     <t>Category Name</t>
@@ -213,7 +213,7 @@
     <t/>
   </si>
   <si>
-    <t>2026-07-27T09:02:16.379Z</t>
+    <t>2026-07-29T03:40:58.474Z</t>
   </si>
   <si>
     <t>MOB-TC-0002</t>
@@ -222,6 +222,9 @@
     <t>Mobile Assertion Verification #2</t>
   </si>
   <si>
+    <t>2026-07-29T03:40:58.475Z</t>
+  </si>
+  <si>
     <t>MOB-TC-0003</t>
   </si>
   <si>
@@ -378,9 +381,6 @@
     <t>Mobile Assertion Verification #28</t>
   </si>
   <si>
-    <t>2026-07-27T09:02:16.380Z</t>
-  </si>
-  <si>
     <t>MOB-TC-0029</t>
   </si>
   <si>
@@ -2077,6 +2077,9 @@
   </si>
   <si>
     <t>Mobile Assertion Verification #311</t>
+  </si>
+  <si>
+    <t>2026-07-29T03:40:58.476Z</t>
   </si>
   <si>
     <t>MOB-TC-0312</t>
@@ -3136,7 +3139,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3156,7 +3159,7 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3176,7 +3179,7 @@
         <v>6</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3256,7 +3259,7 @@
         <v>6</v>
       </c>
       <c r="F8">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3276,7 +3279,7 @@
         <v>6</v>
       </c>
       <c r="F9">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3316,7 +3319,7 @@
         <v>6</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3336,7 +3339,7 @@
         <v>6</v>
       </c>
       <c r="F12">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -3356,7 +3359,7 @@
         <v>6</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -3396,7 +3399,7 @@
         <v>6</v>
       </c>
       <c r="F15">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -3416,7 +3419,7 @@
         <v>6</v>
       </c>
       <c r="F16">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -3436,7 +3439,7 @@
         <v>6</v>
       </c>
       <c r="F17">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -3456,7 +3459,7 @@
         <v>6</v>
       </c>
       <c r="F18">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -3476,7 +3479,7 @@
         <v>6</v>
       </c>
       <c r="F19">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -3496,7 +3499,7 @@
         <v>6</v>
       </c>
       <c r="F20">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -3516,7 +3519,7 @@
         <v>6</v>
       </c>
       <c r="F21">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -3536,7 +3539,7 @@
         <v>6</v>
       </c>
       <c r="F22">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -3576,7 +3579,7 @@
         <v>6</v>
       </c>
       <c r="F24">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -3596,7 +3599,7 @@
         <v>6</v>
       </c>
       <c r="F25">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -3616,7 +3619,7 @@
         <v>6</v>
       </c>
       <c r="F26">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -3636,7 +3639,7 @@
         <v>6</v>
       </c>
       <c r="F27">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -3656,7 +3659,7 @@
         <v>6</v>
       </c>
       <c r="F28">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -3676,7 +3679,7 @@
         <v>6</v>
       </c>
       <c r="F29">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -3696,7 +3699,7 @@
         <v>6</v>
       </c>
       <c r="F30">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -3716,7 +3719,7 @@
         <v>6</v>
       </c>
       <c r="F31">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -3736,7 +3739,7 @@
         <v>6</v>
       </c>
       <c r="F32">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -3756,7 +3759,7 @@
         <v>6</v>
       </c>
       <c r="F33">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -3796,7 +3799,7 @@
         <v>6</v>
       </c>
       <c r="F35">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3816,7 +3819,7 @@
         <v>6</v>
       </c>
       <c r="F36">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3856,7 +3859,7 @@
         <v>6</v>
       </c>
       <c r="F38">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -3876,7 +3879,7 @@
         <v>6</v>
       </c>
       <c r="F39">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -3896,7 +3899,7 @@
         <v>6</v>
       </c>
       <c r="F40">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -3916,7 +3919,7 @@
         <v>6</v>
       </c>
       <c r="F41">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3975,7 +3978,7 @@
         <v>13</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>65</v>
@@ -3998,611 +4001,611 @@
         <v>13</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
         <v>65</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
         <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
         <v>65</v>
       </c>
       <c r="G5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
         <v>65</v>
       </c>
       <c r="G6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
         <v>65</v>
       </c>
       <c r="G7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
         <v>65</v>
       </c>
       <c r="G8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E9">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
         <v>65</v>
       </c>
       <c r="G9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E10">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
         <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E11">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
         <v>65</v>
       </c>
       <c r="G11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B12" t="s">
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E12">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
         <v>65</v>
       </c>
       <c r="G12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E13">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s">
         <v>65</v>
       </c>
       <c r="G13" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B14" t="s">
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" t="s">
         <v>65</v>
       </c>
       <c r="G14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B15" t="s">
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F15" t="s">
         <v>65</v>
       </c>
       <c r="G15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B16" t="s">
         <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E16">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F16" t="s">
         <v>65</v>
       </c>
       <c r="G16" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B17" t="s">
         <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F17" t="s">
         <v>65</v>
       </c>
       <c r="G17" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B18" t="s">
         <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E18">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
         <v>65</v>
       </c>
       <c r="G18" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B19" t="s">
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E19">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F19" t="s">
         <v>65</v>
       </c>
       <c r="G19" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B20" t="s">
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
         <v>65</v>
       </c>
       <c r="G20" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B21" t="s">
         <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E21">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F21" t="s">
         <v>65</v>
       </c>
       <c r="G21" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B22" t="s">
         <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E22">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
         <v>65</v>
       </c>
       <c r="G22" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B23" t="s">
         <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E23">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F23" t="s">
         <v>65</v>
       </c>
       <c r="G23" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B24" t="s">
         <v>19</v>
       </c>
       <c r="C24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E24">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
         <v>65</v>
       </c>
       <c r="G24" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B25" t="s">
         <v>19</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
         <v>65</v>
       </c>
       <c r="G25" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B26" t="s">
         <v>19</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E26">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F26" t="s">
         <v>65</v>
       </c>
       <c r="G26" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B27" t="s">
         <v>19</v>
       </c>
       <c r="C27" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E27">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F27" t="s">
         <v>65</v>
       </c>
       <c r="G27" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B28" t="s">
         <v>19</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E28">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F28" t="s">
         <v>65</v>
       </c>
       <c r="G28" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B29" t="s">
         <v>19</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E29">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
         <v>65</v>
       </c>
       <c r="G29" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -4619,13 +4622,13 @@
         <v>13</v>
       </c>
       <c r="E30">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F30" t="s">
         <v>65</v>
       </c>
       <c r="G30" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -4642,13 +4645,13 @@
         <v>13</v>
       </c>
       <c r="E31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
         <v>65</v>
       </c>
       <c r="G31" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -4665,13 +4668,13 @@
         <v>13</v>
       </c>
       <c r="E32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F32" t="s">
         <v>65</v>
       </c>
       <c r="G32" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -4688,13 +4691,13 @@
         <v>13</v>
       </c>
       <c r="E33">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
         <v>65</v>
       </c>
       <c r="G33" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -4711,13 +4714,13 @@
         <v>13</v>
       </c>
       <c r="E34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F34" t="s">
         <v>65</v>
       </c>
       <c r="G34" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -4734,13 +4737,13 @@
         <v>13</v>
       </c>
       <c r="E35">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F35" t="s">
         <v>65</v>
       </c>
       <c r="G35" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -4757,13 +4760,13 @@
         <v>13</v>
       </c>
       <c r="E36">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F36" t="s">
         <v>65</v>
       </c>
       <c r="G36" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -4780,13 +4783,13 @@
         <v>13</v>
       </c>
       <c r="E37">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F37" t="s">
         <v>65</v>
       </c>
       <c r="G37" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -4803,13 +4806,13 @@
         <v>13</v>
       </c>
       <c r="E38">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F38" t="s">
         <v>65</v>
       </c>
       <c r="G38" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -4826,13 +4829,13 @@
         <v>13</v>
       </c>
       <c r="E39">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F39" t="s">
         <v>65</v>
       </c>
       <c r="G39" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -4849,13 +4852,13 @@
         <v>13</v>
       </c>
       <c r="E40">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F40" t="s">
         <v>65</v>
       </c>
       <c r="G40" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -4872,13 +4875,13 @@
         <v>13</v>
       </c>
       <c r="E41">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F41" t="s">
         <v>65</v>
       </c>
       <c r="G41" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -4895,13 +4898,13 @@
         <v>13</v>
       </c>
       <c r="E42">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F42" t="s">
         <v>65</v>
       </c>
       <c r="G42" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -4918,13 +4921,13 @@
         <v>13</v>
       </c>
       <c r="E43">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F43" t="s">
         <v>65</v>
       </c>
       <c r="G43" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -4941,13 +4944,13 @@
         <v>13</v>
       </c>
       <c r="E44">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F44" t="s">
         <v>65</v>
       </c>
       <c r="G44" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -4964,13 +4967,13 @@
         <v>13</v>
       </c>
       <c r="E45">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F45" t="s">
         <v>65</v>
       </c>
       <c r="G45" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -4993,7 +4996,7 @@
         <v>65</v>
       </c>
       <c r="G46" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -5010,13 +5013,13 @@
         <v>13</v>
       </c>
       <c r="E47">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F47" t="s">
         <v>65</v>
       </c>
       <c r="G47" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -5033,13 +5036,13 @@
         <v>13</v>
       </c>
       <c r="E48">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F48" t="s">
         <v>65</v>
       </c>
       <c r="G48" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -5056,13 +5059,13 @@
         <v>13</v>
       </c>
       <c r="E49">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F49" t="s">
         <v>65</v>
       </c>
       <c r="G49" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -5079,13 +5082,13 @@
         <v>13</v>
       </c>
       <c r="E50">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F50" t="s">
         <v>65</v>
       </c>
       <c r="G50" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -5102,13 +5105,13 @@
         <v>13</v>
       </c>
       <c r="E51">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F51" t="s">
         <v>65</v>
       </c>
       <c r="G51" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -5125,13 +5128,13 @@
         <v>13</v>
       </c>
       <c r="E52">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F52" t="s">
         <v>65</v>
       </c>
       <c r="G52" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -5148,13 +5151,13 @@
         <v>13</v>
       </c>
       <c r="E53">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F53" t="s">
         <v>65</v>
       </c>
       <c r="G53" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -5171,13 +5174,13 @@
         <v>13</v>
       </c>
       <c r="E54">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F54" t="s">
         <v>65</v>
       </c>
       <c r="G54" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -5194,13 +5197,13 @@
         <v>13</v>
       </c>
       <c r="E55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F55" t="s">
         <v>65</v>
       </c>
       <c r="G55" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -5217,13 +5220,13 @@
         <v>13</v>
       </c>
       <c r="E56">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F56" t="s">
         <v>65</v>
       </c>
       <c r="G56" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -5240,13 +5243,13 @@
         <v>13</v>
       </c>
       <c r="E57">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F57" t="s">
         <v>65</v>
       </c>
       <c r="G57" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -5263,13 +5266,13 @@
         <v>13</v>
       </c>
       <c r="E58">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F58" t="s">
         <v>65</v>
       </c>
       <c r="G58" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -5292,7 +5295,7 @@
         <v>65</v>
       </c>
       <c r="G59" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -5309,13 +5312,13 @@
         <v>13</v>
       </c>
       <c r="E60">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F60" t="s">
         <v>65</v>
       </c>
       <c r="G60" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -5332,13 +5335,13 @@
         <v>13</v>
       </c>
       <c r="E61">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F61" t="s">
         <v>65</v>
       </c>
       <c r="G61" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -5355,13 +5358,13 @@
         <v>13</v>
       </c>
       <c r="E62">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F62" t="s">
         <v>65</v>
       </c>
       <c r="G62" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -5384,7 +5387,7 @@
         <v>65</v>
       </c>
       <c r="G63" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -5401,13 +5404,13 @@
         <v>13</v>
       </c>
       <c r="E64">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F64" t="s">
         <v>65</v>
       </c>
       <c r="G64" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -5424,13 +5427,13 @@
         <v>13</v>
       </c>
       <c r="E65">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F65" t="s">
         <v>65</v>
       </c>
       <c r="G65" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -5447,13 +5450,13 @@
         <v>13</v>
       </c>
       <c r="E66">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F66" t="s">
         <v>65</v>
       </c>
       <c r="G66" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -5476,7 +5479,7 @@
         <v>65</v>
       </c>
       <c r="G67" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -5493,13 +5496,13 @@
         <v>13</v>
       </c>
       <c r="E68">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F68" t="s">
         <v>65</v>
       </c>
       <c r="G68" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -5516,13 +5519,13 @@
         <v>13</v>
       </c>
       <c r="E69">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F69" t="s">
         <v>65</v>
       </c>
       <c r="G69" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -5539,13 +5542,13 @@
         <v>13</v>
       </c>
       <c r="E70">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F70" t="s">
         <v>65</v>
       </c>
       <c r="G70" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -5562,13 +5565,13 @@
         <v>13</v>
       </c>
       <c r="E71">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F71" t="s">
         <v>65</v>
       </c>
       <c r="G71" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -5585,13 +5588,13 @@
         <v>13</v>
       </c>
       <c r="E72">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F72" t="s">
         <v>65</v>
       </c>
       <c r="G72" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -5614,7 +5617,7 @@
         <v>65</v>
       </c>
       <c r="G73" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -5631,13 +5634,13 @@
         <v>13</v>
       </c>
       <c r="E74">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F74" t="s">
         <v>65</v>
       </c>
       <c r="G74" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -5654,13 +5657,13 @@
         <v>13</v>
       </c>
       <c r="E75">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F75" t="s">
         <v>65</v>
       </c>
       <c r="G75" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -5677,13 +5680,13 @@
         <v>13</v>
       </c>
       <c r="E76">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F76" t="s">
         <v>65</v>
       </c>
       <c r="G76" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -5700,13 +5703,13 @@
         <v>13</v>
       </c>
       <c r="E77">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F77" t="s">
         <v>65</v>
       </c>
       <c r="G77" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -5723,13 +5726,13 @@
         <v>13</v>
       </c>
       <c r="E78">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F78" t="s">
         <v>65</v>
       </c>
       <c r="G78" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -5752,7 +5755,7 @@
         <v>65</v>
       </c>
       <c r="G79" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -5769,13 +5772,13 @@
         <v>13</v>
       </c>
       <c r="E80">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F80" t="s">
         <v>65</v>
       </c>
       <c r="G80" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -5792,13 +5795,13 @@
         <v>13</v>
       </c>
       <c r="E81">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F81" t="s">
         <v>65</v>
       </c>
       <c r="G81" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -5815,13 +5818,13 @@
         <v>13</v>
       </c>
       <c r="E82">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F82" t="s">
         <v>65</v>
       </c>
       <c r="G82" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -5838,13 +5841,13 @@
         <v>13</v>
       </c>
       <c r="E83">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F83" t="s">
         <v>65</v>
       </c>
       <c r="G83" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -5861,13 +5864,13 @@
         <v>13</v>
       </c>
       <c r="E84">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F84" t="s">
         <v>65</v>
       </c>
       <c r="G84" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -5884,13 +5887,13 @@
         <v>13</v>
       </c>
       <c r="E85">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F85" t="s">
         <v>65</v>
       </c>
       <c r="G85" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -5907,13 +5910,13 @@
         <v>13</v>
       </c>
       <c r="E86">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F86" t="s">
         <v>65</v>
       </c>
       <c r="G86" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -5930,13 +5933,13 @@
         <v>13</v>
       </c>
       <c r="E87">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F87" t="s">
         <v>65</v>
       </c>
       <c r="G87" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -5953,13 +5956,13 @@
         <v>13</v>
       </c>
       <c r="E88">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F88" t="s">
         <v>65</v>
       </c>
       <c r="G88" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -5976,13 +5979,13 @@
         <v>13</v>
       </c>
       <c r="E89">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F89" t="s">
         <v>65</v>
       </c>
       <c r="G89" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -5999,13 +6002,13 @@
         <v>13</v>
       </c>
       <c r="E90">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F90" t="s">
         <v>65</v>
       </c>
       <c r="G90" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -6022,13 +6025,13 @@
         <v>13</v>
       </c>
       <c r="E91">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F91" t="s">
         <v>65</v>
       </c>
       <c r="G91" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -6045,13 +6048,13 @@
         <v>13</v>
       </c>
       <c r="E92">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F92" t="s">
         <v>65</v>
       </c>
       <c r="G92" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -6068,13 +6071,13 @@
         <v>13</v>
       </c>
       <c r="E93">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F93" t="s">
         <v>65</v>
       </c>
       <c r="G93" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -6091,13 +6094,13 @@
         <v>13</v>
       </c>
       <c r="E94">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F94" t="s">
         <v>65</v>
       </c>
       <c r="G94" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -6114,13 +6117,13 @@
         <v>13</v>
       </c>
       <c r="E95">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F95" t="s">
         <v>65</v>
       </c>
       <c r="G95" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -6137,13 +6140,13 @@
         <v>13</v>
       </c>
       <c r="E96">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F96" t="s">
         <v>65</v>
       </c>
       <c r="G96" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -6160,13 +6163,13 @@
         <v>13</v>
       </c>
       <c r="E97">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F97" t="s">
         <v>65</v>
       </c>
       <c r="G97" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -6183,13 +6186,13 @@
         <v>13</v>
       </c>
       <c r="E98">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F98" t="s">
         <v>65</v>
       </c>
       <c r="G98" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -6206,13 +6209,13 @@
         <v>13</v>
       </c>
       <c r="E99">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F99" t="s">
         <v>65</v>
       </c>
       <c r="G99" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -6235,7 +6238,7 @@
         <v>65</v>
       </c>
       <c r="G100" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -6258,7 +6261,7 @@
         <v>65</v>
       </c>
       <c r="G101" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -6275,13 +6278,13 @@
         <v>13</v>
       </c>
       <c r="E102">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F102" t="s">
         <v>65</v>
       </c>
       <c r="G102" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -6298,13 +6301,13 @@
         <v>13</v>
       </c>
       <c r="E103">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F103" t="s">
         <v>65</v>
       </c>
       <c r="G103" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -6321,13 +6324,13 @@
         <v>13</v>
       </c>
       <c r="E104">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F104" t="s">
         <v>65</v>
       </c>
       <c r="G104" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -6344,13 +6347,13 @@
         <v>13</v>
       </c>
       <c r="E105">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F105" t="s">
         <v>65</v>
       </c>
       <c r="G105" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -6367,13 +6370,13 @@
         <v>13</v>
       </c>
       <c r="E106">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F106" t="s">
         <v>65</v>
       </c>
       <c r="G106" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -6390,13 +6393,13 @@
         <v>13</v>
       </c>
       <c r="E107">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F107" t="s">
         <v>65</v>
       </c>
       <c r="G107" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -6413,13 +6416,13 @@
         <v>13</v>
       </c>
       <c r="E108">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F108" t="s">
         <v>65</v>
       </c>
       <c r="G108" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -6436,13 +6439,13 @@
         <v>13</v>
       </c>
       <c r="E109">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F109" t="s">
         <v>65</v>
       </c>
       <c r="G109" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -6459,13 +6462,13 @@
         <v>13</v>
       </c>
       <c r="E110">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F110" t="s">
         <v>65</v>
       </c>
       <c r="G110" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -6482,13 +6485,13 @@
         <v>13</v>
       </c>
       <c r="E111">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F111" t="s">
         <v>65</v>
       </c>
       <c r="G111" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -6505,13 +6508,13 @@
         <v>13</v>
       </c>
       <c r="E112">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F112" t="s">
         <v>65</v>
       </c>
       <c r="G112" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -6528,13 +6531,13 @@
         <v>13</v>
       </c>
       <c r="E113">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F113" t="s">
         <v>65</v>
       </c>
       <c r="G113" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -6551,13 +6554,13 @@
         <v>13</v>
       </c>
       <c r="E114">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F114" t="s">
         <v>65</v>
       </c>
       <c r="G114" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -6580,7 +6583,7 @@
         <v>65</v>
       </c>
       <c r="G115" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -6597,13 +6600,13 @@
         <v>13</v>
       </c>
       <c r="E116">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F116" t="s">
         <v>65</v>
       </c>
       <c r="G116" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -6620,13 +6623,13 @@
         <v>13</v>
       </c>
       <c r="E117">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F117" t="s">
         <v>65</v>
       </c>
       <c r="G117" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -6643,13 +6646,13 @@
         <v>13</v>
       </c>
       <c r="E118">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F118" t="s">
         <v>65</v>
       </c>
       <c r="G118" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -6666,13 +6669,13 @@
         <v>13</v>
       </c>
       <c r="E119">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F119" t="s">
         <v>65</v>
       </c>
       <c r="G119" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
@@ -6689,13 +6692,13 @@
         <v>13</v>
       </c>
       <c r="E120">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F120" t="s">
         <v>65</v>
       </c>
       <c r="G120" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -6712,13 +6715,13 @@
         <v>13</v>
       </c>
       <c r="E121">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F121" t="s">
         <v>65</v>
       </c>
       <c r="G121" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -6735,13 +6738,13 @@
         <v>13</v>
       </c>
       <c r="E122">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F122" t="s">
         <v>65</v>
       </c>
       <c r="G122" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -6758,13 +6761,13 @@
         <v>13</v>
       </c>
       <c r="E123">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F123" t="s">
         <v>65</v>
       </c>
       <c r="G123" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -6781,13 +6784,13 @@
         <v>13</v>
       </c>
       <c r="E124">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F124" t="s">
         <v>65</v>
       </c>
       <c r="G124" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -6804,13 +6807,13 @@
         <v>13</v>
       </c>
       <c r="E125">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F125" t="s">
         <v>65</v>
       </c>
       <c r="G125" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -6827,13 +6830,13 @@
         <v>13</v>
       </c>
       <c r="E126">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F126" t="s">
         <v>65</v>
       </c>
       <c r="G126" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -6850,13 +6853,13 @@
         <v>13</v>
       </c>
       <c r="E127">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F127" t="s">
         <v>65</v>
       </c>
       <c r="G127" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -6879,7 +6882,7 @@
         <v>65</v>
       </c>
       <c r="G128" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -6896,13 +6899,13 @@
         <v>13</v>
       </c>
       <c r="E129">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F129" t="s">
         <v>65</v>
       </c>
       <c r="G129" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -6925,7 +6928,7 @@
         <v>65</v>
       </c>
       <c r="G130" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -6942,13 +6945,13 @@
         <v>13</v>
       </c>
       <c r="E131">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F131" t="s">
         <v>65</v>
       </c>
       <c r="G131" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -6965,13 +6968,13 @@
         <v>13</v>
       </c>
       <c r="E132">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F132" t="s">
         <v>65</v>
       </c>
       <c r="G132" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -6988,13 +6991,13 @@
         <v>13</v>
       </c>
       <c r="E133">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F133" t="s">
         <v>65</v>
       </c>
       <c r="G133" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -7011,13 +7014,13 @@
         <v>13</v>
       </c>
       <c r="E134">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F134" t="s">
         <v>65</v>
       </c>
       <c r="G134" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -7034,13 +7037,13 @@
         <v>13</v>
       </c>
       <c r="E135">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F135" t="s">
         <v>65</v>
       </c>
       <c r="G135" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -7057,13 +7060,13 @@
         <v>13</v>
       </c>
       <c r="E136">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F136" t="s">
         <v>65</v>
       </c>
       <c r="G136" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -7080,13 +7083,13 @@
         <v>13</v>
       </c>
       <c r="E137">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F137" t="s">
         <v>65</v>
       </c>
       <c r="G137" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -7103,13 +7106,13 @@
         <v>13</v>
       </c>
       <c r="E138">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F138" t="s">
         <v>65</v>
       </c>
       <c r="G138" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -7126,13 +7129,13 @@
         <v>13</v>
       </c>
       <c r="E139">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F139" t="s">
         <v>65</v>
       </c>
       <c r="G139" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -7149,13 +7152,13 @@
         <v>13</v>
       </c>
       <c r="E140">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F140" t="s">
         <v>65</v>
       </c>
       <c r="G140" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -7172,13 +7175,13 @@
         <v>13</v>
       </c>
       <c r="E141">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F141" t="s">
         <v>65</v>
       </c>
       <c r="G141" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -7195,13 +7198,13 @@
         <v>13</v>
       </c>
       <c r="E142">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F142" t="s">
         <v>65</v>
       </c>
       <c r="G142" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -7218,13 +7221,13 @@
         <v>13</v>
       </c>
       <c r="E143">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F143" t="s">
         <v>65</v>
       </c>
       <c r="G143" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -7241,13 +7244,13 @@
         <v>13</v>
       </c>
       <c r="E144">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F144" t="s">
         <v>65</v>
       </c>
       <c r="G144" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -7264,13 +7267,13 @@
         <v>13</v>
       </c>
       <c r="E145">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F145" t="s">
         <v>65</v>
       </c>
       <c r="G145" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -7287,13 +7290,13 @@
         <v>13</v>
       </c>
       <c r="E146">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F146" t="s">
         <v>65</v>
       </c>
       <c r="G146" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -7310,13 +7313,13 @@
         <v>13</v>
       </c>
       <c r="E147">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F147" t="s">
         <v>65</v>
       </c>
       <c r="G147" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -7339,7 +7342,7 @@
         <v>65</v>
       </c>
       <c r="G148" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -7356,13 +7359,13 @@
         <v>13</v>
       </c>
       <c r="E149">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F149" t="s">
         <v>65</v>
       </c>
       <c r="G149" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -7379,13 +7382,13 @@
         <v>13</v>
       </c>
       <c r="E150">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F150" t="s">
         <v>65</v>
       </c>
       <c r="G150" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -7402,13 +7405,13 @@
         <v>13</v>
       </c>
       <c r="E151">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F151" t="s">
         <v>65</v>
       </c>
       <c r="G151" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -7425,13 +7428,13 @@
         <v>13</v>
       </c>
       <c r="E152">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F152" t="s">
         <v>65</v>
       </c>
       <c r="G152" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -7448,13 +7451,13 @@
         <v>13</v>
       </c>
       <c r="E153">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F153" t="s">
         <v>65</v>
       </c>
       <c r="G153" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -7471,13 +7474,13 @@
         <v>13</v>
       </c>
       <c r="E154">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F154" t="s">
         <v>65</v>
       </c>
       <c r="G154" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -7494,13 +7497,13 @@
         <v>13</v>
       </c>
       <c r="E155">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F155" t="s">
         <v>65</v>
       </c>
       <c r="G155" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -7517,13 +7520,13 @@
         <v>13</v>
       </c>
       <c r="E156">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F156" t="s">
         <v>65</v>
       </c>
       <c r="G156" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -7540,13 +7543,13 @@
         <v>13</v>
       </c>
       <c r="E157">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F157" t="s">
         <v>65</v>
       </c>
       <c r="G157" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -7563,13 +7566,13 @@
         <v>13</v>
       </c>
       <c r="E158">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F158" t="s">
         <v>65</v>
       </c>
       <c r="G158" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -7586,13 +7589,13 @@
         <v>13</v>
       </c>
       <c r="E159">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F159" t="s">
         <v>65</v>
       </c>
       <c r="G159" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -7609,13 +7612,13 @@
         <v>13</v>
       </c>
       <c r="E160">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F160" t="s">
         <v>65</v>
       </c>
       <c r="G160" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -7632,13 +7635,13 @@
         <v>13</v>
       </c>
       <c r="E161">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F161" t="s">
         <v>65</v>
       </c>
       <c r="G161" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -7655,13 +7658,13 @@
         <v>13</v>
       </c>
       <c r="E162">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F162" t="s">
         <v>65</v>
       </c>
       <c r="G162" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -7678,13 +7681,13 @@
         <v>13</v>
       </c>
       <c r="E163">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F163" t="s">
         <v>65</v>
       </c>
       <c r="G163" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -7701,13 +7704,13 @@
         <v>13</v>
       </c>
       <c r="E164">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F164" t="s">
         <v>65</v>
       </c>
       <c r="G164" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -7724,13 +7727,13 @@
         <v>13</v>
       </c>
       <c r="E165">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F165" t="s">
         <v>65</v>
       </c>
       <c r="G165" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -7747,13 +7750,13 @@
         <v>13</v>
       </c>
       <c r="E166">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F166" t="s">
         <v>65</v>
       </c>
       <c r="G166" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -7770,13 +7773,13 @@
         <v>13</v>
       </c>
       <c r="E167">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F167" t="s">
         <v>65</v>
       </c>
       <c r="G167" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -7793,13 +7796,13 @@
         <v>13</v>
       </c>
       <c r="E168">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F168" t="s">
         <v>65</v>
       </c>
       <c r="G168" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -7816,13 +7819,13 @@
         <v>13</v>
       </c>
       <c r="E169">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F169" t="s">
         <v>65</v>
       </c>
       <c r="G169" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -7839,13 +7842,13 @@
         <v>13</v>
       </c>
       <c r="E170">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F170" t="s">
         <v>65</v>
       </c>
       <c r="G170" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -7862,13 +7865,13 @@
         <v>13</v>
       </c>
       <c r="E171">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F171" t="s">
         <v>65</v>
       </c>
       <c r="G171" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -7885,13 +7888,13 @@
         <v>13</v>
       </c>
       <c r="E172">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F172" t="s">
         <v>65</v>
       </c>
       <c r="G172" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -7908,13 +7911,13 @@
         <v>13</v>
       </c>
       <c r="E173">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F173" t="s">
         <v>65</v>
       </c>
       <c r="G173" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -7931,13 +7934,13 @@
         <v>13</v>
       </c>
       <c r="E174">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F174" t="s">
         <v>65</v>
       </c>
       <c r="G174" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -7960,7 +7963,7 @@
         <v>65</v>
       </c>
       <c r="G175" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -7977,13 +7980,13 @@
         <v>13</v>
       </c>
       <c r="E176">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F176" t="s">
         <v>65</v>
       </c>
       <c r="G176" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -8000,13 +8003,13 @@
         <v>13</v>
       </c>
       <c r="E177">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F177" t="s">
         <v>65</v>
       </c>
       <c r="G177" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -8023,13 +8026,13 @@
         <v>13</v>
       </c>
       <c r="E178">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F178" t="s">
         <v>65</v>
       </c>
       <c r="G178" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -8046,13 +8049,13 @@
         <v>13</v>
       </c>
       <c r="E179">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F179" t="s">
         <v>65</v>
       </c>
       <c r="G179" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -8069,13 +8072,13 @@
         <v>13</v>
       </c>
       <c r="E180">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F180" t="s">
         <v>65</v>
       </c>
       <c r="G180" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -8092,13 +8095,13 @@
         <v>13</v>
       </c>
       <c r="E181">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F181" t="s">
         <v>65</v>
       </c>
       <c r="G181" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -8115,13 +8118,13 @@
         <v>13</v>
       </c>
       <c r="E182">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F182" t="s">
         <v>65</v>
       </c>
       <c r="G182" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -8144,7 +8147,7 @@
         <v>65</v>
       </c>
       <c r="G183" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -8161,13 +8164,13 @@
         <v>13</v>
       </c>
       <c r="E184">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F184" t="s">
         <v>65</v>
       </c>
       <c r="G184" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -8184,13 +8187,13 @@
         <v>13</v>
       </c>
       <c r="E185">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F185" t="s">
         <v>65</v>
       </c>
       <c r="G185" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -8207,13 +8210,13 @@
         <v>13</v>
       </c>
       <c r="E186">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F186" t="s">
         <v>65</v>
       </c>
       <c r="G186" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -8230,13 +8233,13 @@
         <v>13</v>
       </c>
       <c r="E187">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F187" t="s">
         <v>65</v>
       </c>
       <c r="G187" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -8253,13 +8256,13 @@
         <v>13</v>
       </c>
       <c r="E188">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F188" t="s">
         <v>65</v>
       </c>
       <c r="G188" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -8276,13 +8279,13 @@
         <v>13</v>
       </c>
       <c r="E189">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F189" t="s">
         <v>65</v>
       </c>
       <c r="G189" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -8299,13 +8302,13 @@
         <v>13</v>
       </c>
       <c r="E190">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F190" t="s">
         <v>65</v>
       </c>
       <c r="G190" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -8322,13 +8325,13 @@
         <v>13</v>
       </c>
       <c r="E191">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F191" t="s">
         <v>65</v>
       </c>
       <c r="G191" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -8345,13 +8348,13 @@
         <v>13</v>
       </c>
       <c r="E192">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F192" t="s">
         <v>65</v>
       </c>
       <c r="G192" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -8368,13 +8371,13 @@
         <v>13</v>
       </c>
       <c r="E193">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F193" t="s">
         <v>65</v>
       </c>
       <c r="G193" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -8391,13 +8394,13 @@
         <v>13</v>
       </c>
       <c r="E194">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F194" t="s">
         <v>65</v>
       </c>
       <c r="G194" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -8414,13 +8417,13 @@
         <v>13</v>
       </c>
       <c r="E195">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F195" t="s">
         <v>65</v>
       </c>
       <c r="G195" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -8437,13 +8440,13 @@
         <v>13</v>
       </c>
       <c r="E196">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F196" t="s">
         <v>65</v>
       </c>
       <c r="G196" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -8460,13 +8463,13 @@
         <v>13</v>
       </c>
       <c r="E197">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F197" t="s">
         <v>65</v>
       </c>
       <c r="G197" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -8483,13 +8486,13 @@
         <v>13</v>
       </c>
       <c r="E198">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F198" t="s">
         <v>65</v>
       </c>
       <c r="G198" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -8506,13 +8509,13 @@
         <v>13</v>
       </c>
       <c r="E199">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F199" t="s">
         <v>65</v>
       </c>
       <c r="G199" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -8529,13 +8532,13 @@
         <v>13</v>
       </c>
       <c r="E200">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F200" t="s">
         <v>65</v>
       </c>
       <c r="G200" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -8552,13 +8555,13 @@
         <v>13</v>
       </c>
       <c r="E201">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F201" t="s">
         <v>65</v>
       </c>
       <c r="G201" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -8575,13 +8578,13 @@
         <v>13</v>
       </c>
       <c r="E202">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F202" t="s">
         <v>65</v>
       </c>
       <c r="G202" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -8598,13 +8601,13 @@
         <v>13</v>
       </c>
       <c r="E203">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F203" t="s">
         <v>65</v>
       </c>
       <c r="G203" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
@@ -8621,13 +8624,13 @@
         <v>13</v>
       </c>
       <c r="E204">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F204" t="s">
         <v>65</v>
       </c>
       <c r="G204" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -8644,13 +8647,13 @@
         <v>13</v>
       </c>
       <c r="E205">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F205" t="s">
         <v>65</v>
       </c>
       <c r="G205" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -8667,13 +8670,13 @@
         <v>13</v>
       </c>
       <c r="E206">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F206" t="s">
         <v>65</v>
       </c>
       <c r="G206" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
@@ -8690,13 +8693,13 @@
         <v>13</v>
       </c>
       <c r="E207">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F207" t="s">
         <v>65</v>
       </c>
       <c r="G207" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
@@ -8713,13 +8716,13 @@
         <v>13</v>
       </c>
       <c r="E208">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F208" t="s">
         <v>65</v>
       </c>
       <c r="G208" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -8736,13 +8739,13 @@
         <v>13</v>
       </c>
       <c r="E209">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F209" t="s">
         <v>65</v>
       </c>
       <c r="G209" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -8759,13 +8762,13 @@
         <v>13</v>
       </c>
       <c r="E210">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F210" t="s">
         <v>65</v>
       </c>
       <c r="G210" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
@@ -8782,13 +8785,13 @@
         <v>13</v>
       </c>
       <c r="E211">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F211" t="s">
         <v>65</v>
       </c>
       <c r="G211" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -8805,13 +8808,13 @@
         <v>13</v>
       </c>
       <c r="E212">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F212" t="s">
         <v>65</v>
       </c>
       <c r="G212" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -8828,13 +8831,13 @@
         <v>13</v>
       </c>
       <c r="E213">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F213" t="s">
         <v>65</v>
       </c>
       <c r="G213" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -8851,13 +8854,13 @@
         <v>13</v>
       </c>
       <c r="E214">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F214" t="s">
         <v>65</v>
       </c>
       <c r="G214" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -8874,13 +8877,13 @@
         <v>13</v>
       </c>
       <c r="E215">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F215" t="s">
         <v>65</v>
       </c>
       <c r="G215" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
@@ -8897,13 +8900,13 @@
         <v>13</v>
       </c>
       <c r="E216">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F216" t="s">
         <v>65</v>
       </c>
       <c r="G216" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
@@ -8920,13 +8923,13 @@
         <v>13</v>
       </c>
       <c r="E217">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F217" t="s">
         <v>65</v>
       </c>
       <c r="G217" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -8943,13 +8946,13 @@
         <v>13</v>
       </c>
       <c r="E218">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F218" t="s">
         <v>65</v>
       </c>
       <c r="G218" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
@@ -8966,13 +8969,13 @@
         <v>13</v>
       </c>
       <c r="E219">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F219" t="s">
         <v>65</v>
       </c>
       <c r="G219" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
@@ -8989,13 +8992,13 @@
         <v>13</v>
       </c>
       <c r="E220">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F220" t="s">
         <v>65</v>
       </c>
       <c r="G220" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
@@ -9012,13 +9015,13 @@
         <v>13</v>
       </c>
       <c r="E221">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F221" t="s">
         <v>65</v>
       </c>
       <c r="G221" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -9035,13 +9038,13 @@
         <v>13</v>
       </c>
       <c r="E222">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F222" t="s">
         <v>65</v>
       </c>
       <c r="G222" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
@@ -9058,13 +9061,13 @@
         <v>13</v>
       </c>
       <c r="E223">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F223" t="s">
         <v>65</v>
       </c>
       <c r="G223" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
@@ -9081,13 +9084,13 @@
         <v>13</v>
       </c>
       <c r="E224">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F224" t="s">
         <v>65</v>
       </c>
       <c r="G224" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
@@ -9104,13 +9107,13 @@
         <v>13</v>
       </c>
       <c r="E225">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F225" t="s">
         <v>65</v>
       </c>
       <c r="G225" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
@@ -9127,13 +9130,13 @@
         <v>13</v>
       </c>
       <c r="E226">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F226" t="s">
         <v>65</v>
       </c>
       <c r="G226" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
@@ -9150,13 +9153,13 @@
         <v>13</v>
       </c>
       <c r="E227">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F227" t="s">
         <v>65</v>
       </c>
       <c r="G227" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -9173,13 +9176,13 @@
         <v>13</v>
       </c>
       <c r="E228">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F228" t="s">
         <v>65</v>
       </c>
       <c r="G228" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
@@ -9196,13 +9199,13 @@
         <v>13</v>
       </c>
       <c r="E229">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F229" t="s">
         <v>65</v>
       </c>
       <c r="G229" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
@@ -9225,7 +9228,7 @@
         <v>65</v>
       </c>
       <c r="G230" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -9242,13 +9245,13 @@
         <v>13</v>
       </c>
       <c r="E231">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F231" t="s">
         <v>65</v>
       </c>
       <c r="G231" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
@@ -9265,13 +9268,13 @@
         <v>13</v>
       </c>
       <c r="E232">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F232" t="s">
         <v>65</v>
       </c>
       <c r="G232" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
@@ -9294,7 +9297,7 @@
         <v>65</v>
       </c>
       <c r="G233" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -9311,13 +9314,13 @@
         <v>13</v>
       </c>
       <c r="E234">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F234" t="s">
         <v>65</v>
       </c>
       <c r="G234" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -9334,13 +9337,13 @@
         <v>13</v>
       </c>
       <c r="E235">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F235" t="s">
         <v>65</v>
       </c>
       <c r="G235" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
@@ -9357,13 +9360,13 @@
         <v>13</v>
       </c>
       <c r="E236">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F236" t="s">
         <v>65</v>
       </c>
       <c r="G236" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
@@ -9380,13 +9383,13 @@
         <v>13</v>
       </c>
       <c r="E237">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F237" t="s">
         <v>65</v>
       </c>
       <c r="G237" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
@@ -9403,13 +9406,13 @@
         <v>13</v>
       </c>
       <c r="E238">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F238" t="s">
         <v>65</v>
       </c>
       <c r="G238" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
@@ -9426,13 +9429,13 @@
         <v>13</v>
       </c>
       <c r="E239">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F239" t="s">
         <v>65</v>
       </c>
       <c r="G239" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -9449,13 +9452,13 @@
         <v>13</v>
       </c>
       <c r="E240">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F240" t="s">
         <v>65</v>
       </c>
       <c r="G240" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
@@ -9472,13 +9475,13 @@
         <v>13</v>
       </c>
       <c r="E241">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F241" t="s">
         <v>65</v>
       </c>
       <c r="G241" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
@@ -9495,13 +9498,13 @@
         <v>13</v>
       </c>
       <c r="E242">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F242" t="s">
         <v>65</v>
       </c>
       <c r="G242" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
@@ -9518,13 +9521,13 @@
         <v>13</v>
       </c>
       <c r="E243">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F243" t="s">
         <v>65</v>
       </c>
       <c r="G243" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
@@ -9541,13 +9544,13 @@
         <v>13</v>
       </c>
       <c r="E244">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F244" t="s">
         <v>65</v>
       </c>
       <c r="G244" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -9564,13 +9567,13 @@
         <v>13</v>
       </c>
       <c r="E245">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F245" t="s">
         <v>65</v>
       </c>
       <c r="G245" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
@@ -9593,7 +9596,7 @@
         <v>65</v>
       </c>
       <c r="G246" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -9610,13 +9613,13 @@
         <v>13</v>
       </c>
       <c r="E247">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F247" t="s">
         <v>65</v>
       </c>
       <c r="G247" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -9633,13 +9636,13 @@
         <v>13</v>
       </c>
       <c r="E248">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F248" t="s">
         <v>65</v>
       </c>
       <c r="G248" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
@@ -9656,13 +9659,13 @@
         <v>13</v>
       </c>
       <c r="E249">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F249" t="s">
         <v>65</v>
       </c>
       <c r="G249" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
@@ -9679,13 +9682,13 @@
         <v>13</v>
       </c>
       <c r="E250">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F250" t="s">
         <v>65</v>
       </c>
       <c r="G250" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
@@ -9702,13 +9705,13 @@
         <v>13</v>
       </c>
       <c r="E251">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F251" t="s">
         <v>65</v>
       </c>
       <c r="G251" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
@@ -9725,13 +9728,13 @@
         <v>13</v>
       </c>
       <c r="E252">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F252" t="s">
         <v>65</v>
       </c>
       <c r="G252" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
@@ -9748,13 +9751,13 @@
         <v>13</v>
       </c>
       <c r="E253">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F253" t="s">
         <v>65</v>
       </c>
       <c r="G253" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
@@ -9771,13 +9774,13 @@
         <v>13</v>
       </c>
       <c r="E254">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F254" t="s">
         <v>65</v>
       </c>
       <c r="G254" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
@@ -9794,13 +9797,13 @@
         <v>13</v>
       </c>
       <c r="E255">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F255" t="s">
         <v>65</v>
       </c>
       <c r="G255" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
@@ -9817,13 +9820,13 @@
         <v>13</v>
       </c>
       <c r="E256">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F256" t="s">
         <v>65</v>
       </c>
       <c r="G256" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -9840,13 +9843,13 @@
         <v>13</v>
       </c>
       <c r="E257">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F257" t="s">
         <v>65</v>
       </c>
       <c r="G257" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
@@ -9863,13 +9866,13 @@
         <v>13</v>
       </c>
       <c r="E258">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F258" t="s">
         <v>65</v>
       </c>
       <c r="G258" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
@@ -9886,13 +9889,13 @@
         <v>13</v>
       </c>
       <c r="E259">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F259" t="s">
         <v>65</v>
       </c>
       <c r="G259" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
@@ -9909,13 +9912,13 @@
         <v>13</v>
       </c>
       <c r="E260">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F260" t="s">
         <v>65</v>
       </c>
       <c r="G260" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
@@ -9932,13 +9935,13 @@
         <v>13</v>
       </c>
       <c r="E261">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F261" t="s">
         <v>65</v>
       </c>
       <c r="G261" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
@@ -9955,13 +9958,13 @@
         <v>13</v>
       </c>
       <c r="E262">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F262" t="s">
         <v>65</v>
       </c>
       <c r="G262" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
@@ -9978,13 +9981,13 @@
         <v>13</v>
       </c>
       <c r="E263">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F263" t="s">
         <v>65</v>
       </c>
       <c r="G263" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -10007,7 +10010,7 @@
         <v>65</v>
       </c>
       <c r="G264" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
@@ -10024,13 +10027,13 @@
         <v>13</v>
       </c>
       <c r="E265">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F265" t="s">
         <v>65</v>
       </c>
       <c r="G265" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -10047,13 +10050,13 @@
         <v>13</v>
       </c>
       <c r="E266">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F266" t="s">
         <v>65</v>
       </c>
       <c r="G266" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
@@ -10070,13 +10073,13 @@
         <v>13</v>
       </c>
       <c r="E267">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F267" t="s">
         <v>65</v>
       </c>
       <c r="G267" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
@@ -10093,13 +10096,13 @@
         <v>13</v>
       </c>
       <c r="E268">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F268" t="s">
         <v>65</v>
       </c>
       <c r="G268" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
@@ -10116,13 +10119,13 @@
         <v>13</v>
       </c>
       <c r="E269">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F269" t="s">
         <v>65</v>
       </c>
       <c r="G269" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
@@ -10139,13 +10142,13 @@
         <v>13</v>
       </c>
       <c r="E270">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F270" t="s">
         <v>65</v>
       </c>
       <c r="G270" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
@@ -10162,13 +10165,13 @@
         <v>13</v>
       </c>
       <c r="E271">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F271" t="s">
         <v>65</v>
       </c>
       <c r="G271" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
@@ -10185,13 +10188,13 @@
         <v>13</v>
       </c>
       <c r="E272">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F272" t="s">
         <v>65</v>
       </c>
       <c r="G272" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
@@ -10208,13 +10211,13 @@
         <v>13</v>
       </c>
       <c r="E273">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F273" t="s">
         <v>65</v>
       </c>
       <c r="G273" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
@@ -10231,13 +10234,13 @@
         <v>13</v>
       </c>
       <c r="E274">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F274" t="s">
         <v>65</v>
       </c>
       <c r="G274" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
@@ -10254,13 +10257,13 @@
         <v>13</v>
       </c>
       <c r="E275">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F275" t="s">
         <v>65</v>
       </c>
       <c r="G275" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
@@ -10277,13 +10280,13 @@
         <v>13</v>
       </c>
       <c r="E276">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F276" t="s">
         <v>65</v>
       </c>
       <c r="G276" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
@@ -10300,13 +10303,13 @@
         <v>13</v>
       </c>
       <c r="E277">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F277" t="s">
         <v>65</v>
       </c>
       <c r="G277" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
@@ -10323,13 +10326,13 @@
         <v>13</v>
       </c>
       <c r="E278">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F278" t="s">
         <v>65</v>
       </c>
       <c r="G278" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
@@ -10346,13 +10349,13 @@
         <v>13</v>
       </c>
       <c r="E279">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F279" t="s">
         <v>65</v>
       </c>
       <c r="G279" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
@@ -10369,13 +10372,13 @@
         <v>13</v>
       </c>
       <c r="E280">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F280" t="s">
         <v>65</v>
       </c>
       <c r="G280" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
@@ -10392,13 +10395,13 @@
         <v>13</v>
       </c>
       <c r="E281">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F281" t="s">
         <v>65</v>
       </c>
       <c r="G281" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
@@ -10415,13 +10418,13 @@
         <v>13</v>
       </c>
       <c r="E282">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F282" t="s">
         <v>65</v>
       </c>
       <c r="G282" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
@@ -10438,13 +10441,13 @@
         <v>13</v>
       </c>
       <c r="E283">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F283" t="s">
         <v>65</v>
       </c>
       <c r="G283" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
@@ -10461,13 +10464,13 @@
         <v>13</v>
       </c>
       <c r="E284">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F284" t="s">
         <v>65</v>
       </c>
       <c r="G284" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
@@ -10484,13 +10487,13 @@
         <v>13</v>
       </c>
       <c r="E285">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F285" t="s">
         <v>65</v>
       </c>
       <c r="G285" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
@@ -10507,13 +10510,13 @@
         <v>13</v>
       </c>
       <c r="E286">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F286" t="s">
         <v>65</v>
       </c>
       <c r="G286" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
@@ -10530,13 +10533,13 @@
         <v>13</v>
       </c>
       <c r="E287">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F287" t="s">
         <v>65</v>
       </c>
       <c r="G287" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
@@ -10553,13 +10556,13 @@
         <v>13</v>
       </c>
       <c r="E288">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F288" t="s">
         <v>65</v>
       </c>
       <c r="G288" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
@@ -10576,13 +10579,13 @@
         <v>13</v>
       </c>
       <c r="E289">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F289" t="s">
         <v>65</v>
       </c>
       <c r="G289" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
@@ -10599,13 +10602,13 @@
         <v>13</v>
       </c>
       <c r="E290">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F290" t="s">
         <v>65</v>
       </c>
       <c r="G290" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
@@ -10622,13 +10625,13 @@
         <v>13</v>
       </c>
       <c r="E291">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F291" t="s">
         <v>65</v>
       </c>
       <c r="G291" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
@@ -10645,13 +10648,13 @@
         <v>13</v>
       </c>
       <c r="E292">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F292" t="s">
         <v>65</v>
       </c>
       <c r="G292" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
@@ -10668,13 +10671,13 @@
         <v>13</v>
       </c>
       <c r="E293">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F293" t="s">
         <v>65</v>
       </c>
       <c r="G293" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
@@ -10691,13 +10694,13 @@
         <v>13</v>
       </c>
       <c r="E294">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F294" t="s">
         <v>65</v>
       </c>
       <c r="G294" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
@@ -10714,13 +10717,13 @@
         <v>13</v>
       </c>
       <c r="E295">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F295" t="s">
         <v>65</v>
       </c>
       <c r="G295" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
@@ -10737,13 +10740,13 @@
         <v>13</v>
       </c>
       <c r="E296">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F296" t="s">
         <v>65</v>
       </c>
       <c r="G296" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
@@ -10760,13 +10763,13 @@
         <v>13</v>
       </c>
       <c r="E297">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F297" t="s">
         <v>65</v>
       </c>
       <c r="G297" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
@@ -10783,13 +10786,13 @@
         <v>13</v>
       </c>
       <c r="E298">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F298" t="s">
         <v>65</v>
       </c>
       <c r="G298" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
@@ -10806,13 +10809,13 @@
         <v>13</v>
       </c>
       <c r="E299">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F299" t="s">
         <v>65</v>
       </c>
       <c r="G299" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
@@ -10835,7 +10838,7 @@
         <v>65</v>
       </c>
       <c r="G300" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
@@ -10852,13 +10855,13 @@
         <v>13</v>
       </c>
       <c r="E301">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F301" t="s">
         <v>65</v>
       </c>
       <c r="G301" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
@@ -10875,13 +10878,13 @@
         <v>13</v>
       </c>
       <c r="E302">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F302" t="s">
         <v>65</v>
       </c>
       <c r="G302" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.25">
@@ -10898,13 +10901,13 @@
         <v>13</v>
       </c>
       <c r="E303">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F303" t="s">
         <v>65</v>
       </c>
       <c r="G303" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.25">
@@ -10921,13 +10924,13 @@
         <v>13</v>
       </c>
       <c r="E304">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F304" t="s">
         <v>65</v>
       </c>
       <c r="G304" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
@@ -10944,13 +10947,13 @@
         <v>13</v>
       </c>
       <c r="E305">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F305" t="s">
         <v>65</v>
       </c>
       <c r="G305" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.25">
@@ -10967,13 +10970,13 @@
         <v>13</v>
       </c>
       <c r="E306">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F306" t="s">
         <v>65</v>
       </c>
       <c r="G306" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.25">
@@ -10996,7 +10999,7 @@
         <v>65</v>
       </c>
       <c r="G307" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.25">
@@ -11013,13 +11016,13 @@
         <v>13</v>
       </c>
       <c r="E308">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F308" t="s">
         <v>65</v>
       </c>
       <c r="G308" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.25">
@@ -11036,13 +11039,13 @@
         <v>13</v>
       </c>
       <c r="E309">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F309" t="s">
         <v>65</v>
       </c>
       <c r="G309" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.25">
@@ -11059,13 +11062,13 @@
         <v>13</v>
       </c>
       <c r="E310">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F310" t="s">
         <v>65</v>
       </c>
       <c r="G310" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">
@@ -11082,13 +11085,13 @@
         <v>13</v>
       </c>
       <c r="E311">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F311" t="s">
         <v>65</v>
       </c>
       <c r="G311" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
@@ -11105,415 +11108,415 @@
         <v>13</v>
       </c>
       <c r="E312">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F312" t="s">
         <v>65</v>
       </c>
       <c r="G312" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B313" t="s">
         <v>48</v>
       </c>
       <c r="C313" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D313" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E313">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F313" t="s">
         <v>65</v>
       </c>
       <c r="G313" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B314" t="s">
         <v>48</v>
       </c>
       <c r="C314" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D314" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E314">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F314" t="s">
         <v>65</v>
       </c>
       <c r="G314" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B315" t="s">
         <v>48</v>
       </c>
       <c r="C315" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D315" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E315">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F315" t="s">
         <v>65</v>
       </c>
       <c r="G315" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B316" t="s">
         <v>48</v>
       </c>
       <c r="C316" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E316">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F316" t="s">
         <v>65</v>
       </c>
       <c r="G316" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B317" t="s">
         <v>48</v>
       </c>
       <c r="C317" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D317" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E317">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F317" t="s">
         <v>65</v>
       </c>
       <c r="G317" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B318" t="s">
         <v>48</v>
       </c>
       <c r="C318" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D318" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E318">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F318" t="s">
         <v>65</v>
       </c>
       <c r="G318" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B319" t="s">
         <v>48</v>
       </c>
       <c r="C319" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D319" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E319">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F319" t="s">
         <v>65</v>
       </c>
       <c r="G319" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B320" t="s">
         <v>48</v>
       </c>
       <c r="C320" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D320" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E320">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F320" t="s">
         <v>65</v>
       </c>
       <c r="G320" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B321" t="s">
         <v>48</v>
       </c>
       <c r="C321" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E321">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F321" t="s">
         <v>65</v>
       </c>
       <c r="G321" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B322" t="s">
         <v>49</v>
       </c>
       <c r="C322" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E322">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F322" t="s">
         <v>65</v>
       </c>
       <c r="G322" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B323" t="s">
         <v>49</v>
       </c>
       <c r="C323" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D323" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E323">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F323" t="s">
         <v>65</v>
       </c>
       <c r="G323" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B324" t="s">
         <v>49</v>
       </c>
       <c r="C324" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E324">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F324" t="s">
         <v>65</v>
       </c>
       <c r="G324" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B325" t="s">
         <v>49</v>
       </c>
       <c r="C325" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E325">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F325" t="s">
         <v>65</v>
       </c>
       <c r="G325" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B326" t="s">
         <v>49</v>
       </c>
       <c r="C326" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D326" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E326">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F326" t="s">
         <v>65</v>
       </c>
       <c r="G326" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B327" t="s">
         <v>49</v>
       </c>
       <c r="C327" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D327" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E327">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F327" t="s">
         <v>65</v>
       </c>
       <c r="G327" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B328" t="s">
         <v>49</v>
       </c>
       <c r="C328" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D328" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E328">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F328" t="s">
         <v>65</v>
       </c>
       <c r="G328" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B329" t="s">
         <v>49</v>
       </c>
       <c r="C329" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E329">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F329" t="s">
         <v>65</v>
       </c>
       <c r="G329" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B330" t="s">
         <v>49</v>
       </c>
       <c r="C330" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D330" s="4" t="s">
         <v>13</v>
@@ -11525,317 +11528,317 @@
         <v>65</v>
       </c>
       <c r="G330" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B331" t="s">
         <v>49</v>
       </c>
       <c r="C331" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E331">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F331" t="s">
         <v>65</v>
       </c>
       <c r="G331" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B332" t="s">
         <v>50</v>
       </c>
       <c r="C332" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D332" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E332">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F332" t="s">
         <v>65</v>
       </c>
       <c r="G332" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B333" t="s">
         <v>50</v>
       </c>
       <c r="C333" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E333">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F333" t="s">
         <v>65</v>
       </c>
       <c r="G333" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B334" t="s">
         <v>50</v>
       </c>
       <c r="C334" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D334" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E334">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F334" t="s">
         <v>65</v>
       </c>
       <c r="G334" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B335" t="s">
         <v>50</v>
       </c>
       <c r="C335" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E335">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F335" t="s">
         <v>65</v>
       </c>
       <c r="G335" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B336" t="s">
         <v>50</v>
       </c>
       <c r="C336" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E336">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F336" t="s">
         <v>65</v>
       </c>
       <c r="G336" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B337" t="s">
         <v>50</v>
       </c>
       <c r="C337" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E337">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F337" t="s">
         <v>65</v>
       </c>
       <c r="G337" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B338" t="s">
         <v>50</v>
       </c>
       <c r="C338" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E338">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F338" t="s">
         <v>65</v>
       </c>
       <c r="G338" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B339" t="s">
         <v>50</v>
       </c>
       <c r="C339" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E339">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F339" t="s">
         <v>65</v>
       </c>
       <c r="G339" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B340" t="s">
         <v>50</v>
       </c>
       <c r="C340" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E340">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F340" t="s">
         <v>65</v>
       </c>
       <c r="G340" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B341" t="s">
         <v>50</v>
       </c>
       <c r="C341" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D341" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E341">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F341" t="s">
         <v>65</v>
       </c>
       <c r="G341" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B342" t="s">
         <v>51</v>
       </c>
       <c r="C342" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D342" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E342">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F342" t="s">
         <v>65</v>
       </c>
       <c r="G342" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B343" t="s">
         <v>51</v>
       </c>
       <c r="C343" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D343" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E343">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F343" t="s">
         <v>65</v>
       </c>
       <c r="G343" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B344" t="s">
         <v>51</v>
       </c>
       <c r="C344" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D344" s="4" t="s">
         <v>13</v>
@@ -11847,1007 +11850,1007 @@
         <v>65</v>
       </c>
       <c r="G344" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B345" t="s">
         <v>51</v>
       </c>
       <c r="C345" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E345">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F345" t="s">
         <v>65</v>
       </c>
       <c r="G345" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B346" t="s">
         <v>51</v>
       </c>
       <c r="C346" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D346" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E346">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F346" t="s">
         <v>65</v>
       </c>
       <c r="G346" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B347" t="s">
         <v>51</v>
       </c>
       <c r="C347" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D347" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E347">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F347" t="s">
         <v>65</v>
       </c>
       <c r="G347" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B348" t="s">
         <v>51</v>
       </c>
       <c r="C348" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D348" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E348">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F348" t="s">
         <v>65</v>
       </c>
       <c r="G348" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B349" t="s">
         <v>51</v>
       </c>
       <c r="C349" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D349" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E349">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F349" t="s">
         <v>65</v>
       </c>
       <c r="G349" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B350" t="s">
         <v>51</v>
       </c>
       <c r="C350" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E350">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F350" t="s">
         <v>65</v>
       </c>
       <c r="G350" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B351" t="s">
         <v>51</v>
       </c>
       <c r="C351" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E351">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F351" t="s">
         <v>65</v>
       </c>
       <c r="G351" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B352" t="s">
         <v>52</v>
       </c>
       <c r="C352" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E352">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F352" t="s">
         <v>65</v>
       </c>
       <c r="G352" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B353" t="s">
         <v>52</v>
       </c>
       <c r="C353" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E353">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F353" t="s">
         <v>65</v>
       </c>
       <c r="G353" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B354" t="s">
         <v>52</v>
       </c>
       <c r="C354" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E354">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F354" t="s">
         <v>65</v>
       </c>
       <c r="G354" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B355" t="s">
         <v>52</v>
       </c>
       <c r="C355" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E355">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F355" t="s">
         <v>65</v>
       </c>
       <c r="G355" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B356" t="s">
         <v>52</v>
       </c>
       <c r="C356" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E356">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F356" t="s">
         <v>65</v>
       </c>
       <c r="G356" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B357" t="s">
         <v>52</v>
       </c>
       <c r="C357" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E357">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F357" t="s">
         <v>65</v>
       </c>
       <c r="G357" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B358" t="s">
         <v>52</v>
       </c>
       <c r="C358" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E358">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F358" t="s">
         <v>65</v>
       </c>
       <c r="G358" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B359" t="s">
         <v>52</v>
       </c>
       <c r="C359" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E359">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F359" t="s">
         <v>65</v>
       </c>
       <c r="G359" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B360" t="s">
         <v>52</v>
       </c>
       <c r="C360" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E360">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F360" t="s">
         <v>65</v>
       </c>
       <c r="G360" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B361" t="s">
         <v>52</v>
       </c>
       <c r="C361" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E361">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F361" t="s">
         <v>65</v>
       </c>
       <c r="G361" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B362" t="s">
         <v>53</v>
       </c>
       <c r="C362" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E362">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F362" t="s">
         <v>65</v>
       </c>
       <c r="G362" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B363" t="s">
         <v>53</v>
       </c>
       <c r="C363" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E363">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F363" t="s">
         <v>65</v>
       </c>
       <c r="G363" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B364" t="s">
         <v>53</v>
       </c>
       <c r="C364" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D364" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E364">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F364" t="s">
         <v>65</v>
       </c>
       <c r="G364" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B365" t="s">
         <v>53</v>
       </c>
       <c r="C365" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E365">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F365" t="s">
         <v>65</v>
       </c>
       <c r="G365" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B366" t="s">
         <v>53</v>
       </c>
       <c r="C366" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E366">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F366" t="s">
         <v>65</v>
       </c>
       <c r="G366" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B367" t="s">
         <v>53</v>
       </c>
       <c r="C367" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E367">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F367" t="s">
         <v>65</v>
       </c>
       <c r="G367" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B368" t="s">
         <v>53</v>
       </c>
       <c r="C368" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E368">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F368" t="s">
         <v>65</v>
       </c>
       <c r="G368" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B369" t="s">
         <v>53</v>
       </c>
       <c r="C369" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E369">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F369" t="s">
         <v>65</v>
       </c>
       <c r="G369" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B370" t="s">
         <v>53</v>
       </c>
       <c r="C370" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E370">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F370" t="s">
         <v>65</v>
       </c>
       <c r="G370" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B371" t="s">
         <v>53</v>
       </c>
       <c r="C371" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E371">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F371" t="s">
         <v>65</v>
       </c>
       <c r="G371" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B372" t="s">
         <v>54</v>
       </c>
       <c r="C372" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E372">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F372" t="s">
         <v>65</v>
       </c>
       <c r="G372" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B373" t="s">
         <v>54</v>
       </c>
       <c r="C373" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E373">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F373" t="s">
         <v>65</v>
       </c>
       <c r="G373" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B374" t="s">
         <v>54</v>
       </c>
       <c r="C374" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E374">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F374" t="s">
         <v>65</v>
       </c>
       <c r="G374" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B375" t="s">
         <v>54</v>
       </c>
       <c r="C375" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E375">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F375" t="s">
         <v>65</v>
       </c>
       <c r="G375" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B376" t="s">
         <v>54</v>
       </c>
       <c r="C376" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E376">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F376" t="s">
         <v>65</v>
       </c>
       <c r="G376" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B377" t="s">
         <v>54</v>
       </c>
       <c r="C377" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E377">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F377" t="s">
         <v>65</v>
       </c>
       <c r="G377" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B378" t="s">
         <v>54</v>
       </c>
       <c r="C378" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E378">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F378" t="s">
         <v>65</v>
       </c>
       <c r="G378" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B379" t="s">
         <v>54</v>
       </c>
       <c r="C379" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E379">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F379" t="s">
         <v>65</v>
       </c>
       <c r="G379" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B380" t="s">
         <v>54</v>
       </c>
       <c r="C380" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E380">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F380" t="s">
         <v>65</v>
       </c>
       <c r="G380" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="381" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B381" t="s">
         <v>54</v>
       </c>
       <c r="C381" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E381">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F381" t="s">
         <v>65</v>
       </c>
       <c r="G381" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B382" t="s">
         <v>55</v>
       </c>
       <c r="C382" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D382" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E382">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F382" t="s">
         <v>65</v>
       </c>
       <c r="G382" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B383" t="s">
         <v>55</v>
       </c>
       <c r="C383" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E383">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F383" t="s">
         <v>65</v>
       </c>
       <c r="G383" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B384" t="s">
         <v>55</v>
       </c>
       <c r="C384" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E384">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F384" t="s">
         <v>65</v>
       </c>
       <c r="G384" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B385" t="s">
         <v>55</v>
       </c>
       <c r="C385" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E385">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F385" t="s">
         <v>65</v>
       </c>
       <c r="G385" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B386" t="s">
         <v>55</v>
       </c>
       <c r="C386" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E386">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F386" t="s">
         <v>65</v>
       </c>
       <c r="G386" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B387" t="s">
         <v>55</v>
       </c>
       <c r="C387" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E387">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F387" t="s">
         <v>65</v>
       </c>
       <c r="G387" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B388" t="s">
         <v>55</v>
       </c>
       <c r="C388" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>13</v>
@@ -12859,306 +12862,306 @@
         <v>65</v>
       </c>
       <c r="G388" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B389" t="s">
         <v>55</v>
       </c>
       <c r="C389" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E389">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F389" t="s">
         <v>65</v>
       </c>
       <c r="G389" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B390" t="s">
         <v>55</v>
       </c>
       <c r="C390" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E390">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F390" t="s">
         <v>65</v>
       </c>
       <c r="G390" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B391" t="s">
         <v>55</v>
       </c>
       <c r="C391" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E391">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F391" t="s">
         <v>65</v>
       </c>
       <c r="G391" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B392" t="s">
         <v>56</v>
       </c>
       <c r="C392" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E392">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F392" t="s">
         <v>65</v>
       </c>
       <c r="G392" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B393" t="s">
         <v>56</v>
       </c>
       <c r="C393" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E393">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F393" t="s">
         <v>65</v>
       </c>
       <c r="G393" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B394" t="s">
         <v>56</v>
       </c>
       <c r="C394" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E394">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F394" t="s">
         <v>65</v>
       </c>
       <c r="G394" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="395" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B395" t="s">
         <v>56</v>
       </c>
       <c r="C395" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E395">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F395" t="s">
         <v>65</v>
       </c>
       <c r="G395" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B396" t="s">
         <v>56</v>
       </c>
       <c r="C396" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D396" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E396">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F396" t="s">
         <v>65</v>
       </c>
       <c r="G396" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B397" t="s">
         <v>56</v>
       </c>
       <c r="C397" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D397" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E397">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F397" t="s">
         <v>65</v>
       </c>
       <c r="G397" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B398" t="s">
         <v>56</v>
       </c>
       <c r="C398" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E398">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F398" t="s">
         <v>65</v>
       </c>
       <c r="G398" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B399" t="s">
         <v>56</v>
       </c>
       <c r="C399" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E399">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F399" t="s">
         <v>65</v>
       </c>
       <c r="G399" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B400" t="s">
         <v>56</v>
       </c>
       <c r="C400" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E400">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F400" t="s">
         <v>65</v>
       </c>
       <c r="G400" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
     <row r="401" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B401" t="s">
         <v>56</v>
       </c>
       <c r="C401" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E401">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F401" t="s">
         <v>65</v>
       </c>
       <c r="G401" t="s">
-        <v>121</v>
+        <v>688</v>
       </c>
     </row>
   </sheetData>
